--- a/data-raw/fsaArcPlc/input_data/fsaMyaPrice/MYA_2026.xlsx
+++ b/data-raw/fsaArcPlc/input_data/fsaMyaPrice/MYA_2026.xlsx
@@ -1,31 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="S:\EPAS\2014FBIMP\ARC_PLC\Webpage Posting\2026-0520\Program Year 2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="S:\EPAS\2014FBIMP\ARC_PLC\Webpage Posting\2026-0812\Program Year 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{030D6E40-DD42-40F9-8B51-514DAAB34110}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D1BECF1-3C55-4774-83CE-31B571A8333C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MYA Prices" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0" concurrentCalc="0"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="55">
   <si>
     <t>TABLE 1. 2020/21-2026/27 MARKET YEAR AVERAGE (MYA) PRICES</t>
   </si>
   <si>
-    <t>May 20, 2026 1/</t>
+    <t>August 12, 2026 1/</t>
   </si>
   <si>
     <t>Commodity</t>
@@ -71,6 +71,9 @@
   </si>
   <si>
     <t>Bushel</t>
+  </si>
+  <si>
+    <t>F</t>
   </si>
   <si>
     <t>P</t>
@@ -682,21 +685,21 @@
         <v>5.52</v>
       </c>
       <c r="J5" s="5">
-        <v>5</v>
+        <v>5.0599999999999996</v>
       </c>
       <c r="K5" s="7" t="s">
         <v>17</v>
       </c>
       <c r="L5" s="6">
-        <v>6.5</v>
+        <v>6.2</v>
       </c>
       <c r="M5" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>14</v>
@@ -723,7 +726,7 @@
         <v>6.31</v>
       </c>
       <c r="J6" s="5">
-        <v>5.45</v>
+        <v>5.46</v>
       </c>
       <c r="K6" s="7" t="s">
         <v>17</v>
@@ -732,12 +735,12 @@
         <v>5.6</v>
       </c>
       <c r="M6" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>14</v>
@@ -764,7 +767,7 @@
         <v>3.35</v>
       </c>
       <c r="J7" s="5">
-        <v>3.25</v>
+        <v>3.23</v>
       </c>
       <c r="K7" s="7" t="s">
         <v>17</v>
@@ -773,21 +776,21 @@
         <v>3.35</v>
       </c>
       <c r="M7" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E8" s="8">
         <v>0.21</v>
@@ -805,27 +808,27 @@
         <v>0.26100000000000001</v>
       </c>
       <c r="J8" s="8">
-        <v>0.23300000000000001</v>
+        <v>0.23599999999999999</v>
       </c>
       <c r="K8" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L8" s="9">
         <v>0.24</v>
       </c>
       <c r="M8" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>16</v>
@@ -849,24 +852,24 @@
         <v>4.1500000000000004</v>
       </c>
       <c r="K9" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L9" s="6">
-        <v>4.4000000000000004</v>
+        <v>4.5</v>
       </c>
       <c r="M9" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" s="4" t="s">
         <v>27</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>26</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>16</v>
@@ -890,24 +893,24 @@
         <v>3.55</v>
       </c>
       <c r="K10" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L10" s="6">
-        <v>4.0999999999999996</v>
+        <v>4.3</v>
       </c>
       <c r="M10" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>16</v>
@@ -931,27 +934,27 @@
         <v>10.4</v>
       </c>
       <c r="K11" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L11" s="6">
         <v>11.4</v>
       </c>
       <c r="M11" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E12" s="8">
         <v>9.8400000000000001E-2</v>
@@ -969,30 +972,30 @@
         <v>0.13600000000000001</v>
       </c>
       <c r="J12" s="8">
-        <v>0.113</v>
+        <v>0.111</v>
       </c>
       <c r="K12" s="7" t="s">
         <v>17</v>
       </c>
       <c r="L12" s="9">
-        <v>0.123</v>
+        <v>0.113</v>
       </c>
       <c r="M12" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="13" spans="1:13" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C13" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="B13" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>31</v>
-      </c>
       <c r="D13" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E13" s="8">
         <v>0.182</v>
@@ -1010,30 +1013,30 @@
         <v>0.35899999999999999</v>
       </c>
       <c r="J13" s="8">
-        <v>0.22700000000000001</v>
+        <v>0.22</v>
       </c>
       <c r="K13" s="7" t="s">
         <v>17</v>
       </c>
       <c r="L13" s="9">
-        <v>0.248</v>
+        <v>0.21099999999999999</v>
       </c>
       <c r="M13" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E14" s="8">
         <v>0.184</v>
@@ -1051,30 +1054,30 @@
         <v>0.20200000000000001</v>
       </c>
       <c r="J14" s="8">
-        <v>0.20799999999999999</v>
+        <v>0.21099999999999999</v>
       </c>
       <c r="K14" s="7" t="s">
         <v>17</v>
       </c>
       <c r="L14" s="9">
-        <v>0.25</v>
+        <v>0.245</v>
       </c>
       <c r="M14" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="15" spans="1:13" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E15" s="8">
         <v>0.23300000000000001</v>
@@ -1092,30 +1095,30 @@
         <v>0.34300000000000003</v>
       </c>
       <c r="J15" s="8">
-        <v>0.247</v>
+        <v>0.25600000000000001</v>
       </c>
       <c r="K15" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L15" s="9">
-        <v>0.245</v>
+        <v>0.246</v>
       </c>
       <c r="M15" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E16" s="8">
         <v>0.20200000000000001</v>
@@ -1133,30 +1136,30 @@
         <v>0.25600000000000001</v>
       </c>
       <c r="J16" s="8">
-        <v>0.16200000000000001</v>
+        <v>0.16300000000000001</v>
       </c>
       <c r="K16" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L16" s="9">
-        <v>0.16400000000000001</v>
+        <v>0.16600000000000001</v>
       </c>
       <c r="M16" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="17" spans="1:13" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E17" s="8">
         <v>0.21299999999999999</v>
@@ -1174,27 +1177,27 @@
         <v>0.23799999999999999</v>
       </c>
       <c r="J17" s="8">
-        <v>0.24049999999999999</v>
+        <v>0.23499999999999999</v>
       </c>
       <c r="K17" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L17" s="9">
-        <v>0.252</v>
+        <v>0.247</v>
       </c>
       <c r="M17" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="18" spans="1:13" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D18" s="4" t="s">
         <v>16</v>
@@ -1215,30 +1218,30 @@
         <v>12.5</v>
       </c>
       <c r="J18" s="8">
-        <v>12.65</v>
+        <v>12.6</v>
       </c>
       <c r="K18" s="7" t="s">
         <v>17</v>
       </c>
       <c r="L18" s="9">
-        <v>12.88</v>
+        <v>13</v>
       </c>
       <c r="M18" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="19" spans="1:13" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E19" s="8">
         <v>0.26700000000000002</v>
@@ -1256,30 +1259,30 @@
         <v>0.44900000000000001</v>
       </c>
       <c r="J19" s="8">
-        <v>0.313</v>
+        <v>0.3075</v>
       </c>
       <c r="K19" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L19" s="9">
-        <v>0.32200000000000001</v>
+        <v>0.317</v>
       </c>
       <c r="M19" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="20" spans="1:13" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E20" s="8">
         <v>0.22600000000000001</v>
@@ -1303,24 +1306,24 @@
         <v>17</v>
       </c>
       <c r="L20" s="9">
-        <v>0.31</v>
+        <v>0.30499999999999999</v>
       </c>
       <c r="M20" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="21" spans="1:13" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E21" s="8">
         <v>0.215</v>
@@ -1341,27 +1344,27 @@
         <v>0.20799999999999999</v>
       </c>
       <c r="K21" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L21" s="9">
-        <v>0.22</v>
+        <v>0.215</v>
       </c>
       <c r="M21" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="22" spans="1:13" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E22" s="8">
         <v>0.27100000000000002</v>
@@ -1382,27 +1385,27 @@
         <v>0.32</v>
       </c>
       <c r="K22" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L22" s="9">
-        <v>0.372</v>
+        <v>0.36599999999999999</v>
       </c>
       <c r="M22" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="23" spans="1:13" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E23" s="8">
         <v>0.37</v>
@@ -1423,27 +1426,27 @@
         <v>0.33</v>
       </c>
       <c r="K23" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L23" s="9">
         <v>0.38</v>
       </c>
       <c r="M23" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="24" spans="1:13" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E24" s="8">
         <v>0.33929999999999999</v>
@@ -1461,30 +1464,30 @@
         <v>0.34039999999999998</v>
       </c>
       <c r="J24" s="8">
-        <v>0.34549999999999997</v>
+        <v>0.33889999999999998</v>
       </c>
       <c r="K24" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L24" s="9">
-        <v>0.39119999999999999</v>
+        <v>0.40310000000000001</v>
       </c>
       <c r="M24" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="25" spans="1:13" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E25" s="8">
         <v>0.126</v>
@@ -1505,27 +1508,27 @@
         <v>0.104</v>
       </c>
       <c r="K25" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L25" s="9">
-        <v>0.12</v>
+        <v>0.13500000000000001</v>
       </c>
       <c r="M25" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="26" spans="1:13" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C26" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="B26" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>45</v>
-      </c>
       <c r="D26" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E26" s="8">
         <v>0.13100000000000001</v>
@@ -1543,30 +1546,30 @@
         <v>0.15</v>
       </c>
       <c r="J26" s="8">
-        <v>0.14699999999999999</v>
+        <v>0.14899999999999999</v>
       </c>
       <c r="K26" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L26" s="9">
-        <v>0.13500000000000001</v>
+        <v>0.15</v>
       </c>
       <c r="M26" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="27" spans="1:13" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="10" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D27" s="11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E27" s="12">
         <v>0.22600000000000001</v>
@@ -1584,21 +1587,21 @@
         <v>0.187</v>
       </c>
       <c r="J27" s="12">
-        <v>0.20300000000000001</v>
+        <v>0.20200000000000001</v>
       </c>
       <c r="K27" s="14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L27" s="13">
-        <v>0.2</v>
+        <v>0.20499999999999999</v>
       </c>
       <c r="M27" s="14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="29" spans="1:13" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="17" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B29" s="17"/>
       <c r="C29" s="17"/>
@@ -1615,7 +1618,7 @@
     </row>
     <row r="30" spans="1:13" ht="26.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="17" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B30" s="17"/>
       <c r="C30" s="17"/>
@@ -1632,7 +1635,7 @@
     </row>
     <row r="31" spans="1:13" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="17" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B31" s="17"/>
       <c r="C31" s="17"/>
@@ -1649,7 +1652,7 @@
     </row>
     <row r="32" spans="1:13" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="17" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B32" s="17"/>
       <c r="C32" s="17"/>
